--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,140 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2242</v>
       </c>
-      <c r="N2" t="n">
-        <v>39.63131313131314</v>
-      </c>
       <c r="O2" t="n">
+        <v>2242</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1.049808956192257</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -690,99 +878,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1971</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>445.0645161290323</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0.9229141180441293</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -809,99 +1037,214 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2402</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>600.5</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.124728417829527</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Meningitis</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -928,97 +1271,140 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2529</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>571.0645161290322</v>
+        <v>1971</v>
       </c>
       <c r="O5" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.184195740504111</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>0.9229141180441293</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1047,99 +1433,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>2268</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>529.1999999999999</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.061983368708313</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>ftp_dbc</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1166,99 +1592,214 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1397</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>315.4516129032258</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.6541405494204203</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>sinan_datasus</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Brazil DATASUS SINAN</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Meningitis</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1285,97 +1826,2435 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>D235</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2402</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2402</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.124728417829527</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2529</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2529</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.184195740504111</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2268</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2268</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.061983368708313</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1397</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6541405494204203</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1397</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1397</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N19" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="O19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R19" t="n">
         <v>0.004214219717096481</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1493,62 +4372,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12818</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>12857</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>7</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1482,9 +1479,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2037,9 +2031,6 @@
       <c r="O9" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2430,9 +2421,6 @@
       <c r="O11" t="n">
         <v>2529</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>1.184195740504111</v>
       </c>
@@ -2592,9 +2580,6 @@
       <c r="O12" t="n">
         <v>8</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2985,9 +2970,6 @@
       <c r="O14" t="n">
         <v>2268</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>1.061983368708313</v>
       </c>
@@ -3147,9 +3129,6 @@
       <c r="O15" t="n">
         <v>10</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3540,9 +3519,6 @@
       <c r="O17" t="n">
         <v>1397</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.6541405494204203</v>
       </c>
@@ -3935,9 +3911,6 @@
       </c>
       <c r="O19" t="n">
         <v>9</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.004214219717096481</v>

--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -3868,12 +3868,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3898,31 +3898,28 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.004214219717096481</v>
+        <v>16</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3932,7 +3929,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -3942,12 +3939,12 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -3955,47 +3952,47 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4024,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4057,33 +4054,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>SRC_BR_SINAN</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4113,7 +4110,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>country:BR:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -4133,7 +4130,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -4148,12 +4145,12 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>BR_SINAN_MENI_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+          <t>PHO IDTO current-year monthly preliminary meningitis notifications without an etiology qualifier; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -4166,7 +4163,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4176,12 +4173,12 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_CA_ON_PHO_IDTO_MENINGITIS_ALL_ETIOLOGIES_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -4189,45 +4186,438 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.004214219717096481</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV20" t="inlineStr">
+      <c r="AV21" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="BA20" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4349,7 +4739,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -4359,7 +4749,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -4379,7 +4769,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -4411,7 +4801,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12857</v>
+        <v>12873</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d235/2026-2029.xlsx
+++ b/diseases/d235/2026-2029.xlsx
@@ -3514,13 +3514,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1397</v>
+        <v>2489</v>
       </c>
       <c r="O17" t="n">
-        <v>1397</v>
+        <v>2489</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6541405494204203</v>
+        <v>1.165465875094793</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1397</v>
+        <v>2489</v>
       </c>
       <c r="O18" t="n">
-        <v>1397</v>
+        <v>2489</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>1597</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>1597</v>
       </c>
       <c r="R21" t="n">
-        <v>0.004214219717096481</v>
+        <v>0.7477898764670088</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>1597</v>
       </c>
       <c r="O22" t="n">
-        <v>9</v>
+        <v>1597</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -4618,6 +4618,399 @@
         </is>
       </c>
       <c r="BC22" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.004682466352329423</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>meningitis-(all-reported-etiologies)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -4656,7 +5049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -4739,7 +5132,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -4749,7 +5142,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -4769,7 +5162,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -4801,7 +5194,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12873</v>
+        <v>15563</v>
       </c>
     </row>
     <row r="16">
